--- a/data/leaves.xlsx
+++ b/data/leaves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,6 +658,41 @@
         </is>
       </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>已批准</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>年假</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>跨月年假（5月2天，6月2天）</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>已批准</t>
         </is>
